--- a/Cleaning/Dcumentation.xlsx
+++ b/Cleaning/Dcumentation.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\Excel Portfolio\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\Excel Portfolio\Customer Churn Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{07874A33-F51A-49C1-98BF-A5FDF36C402B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D40FBA64-66A7-4242-B11D-672A6A46A8AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{6ADBC9CF-CBD1-4ED1-917A-C73C89460D12}"/>
+    <workbookView xWindow="20" yWindow="740" windowWidth="19180" windowHeight="10060" xr2:uid="{6ADBC9CF-CBD1-4ED1-917A-C73C89460D12}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="80">
   <si>
     <t>Customer_ID</t>
   </si>
@@ -283,6 +283,9 @@
   </si>
   <si>
     <t>Result</t>
+  </si>
+  <si>
+    <t>Error Density</t>
   </si>
 </sst>
 </file>
@@ -332,7 +335,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -348,6 +351,7 @@
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -647,8 +651,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{F9822EF2-40E4-4A6A-8A77-3DA3D90414BC}" name="Table4" displayName="Table4" ref="A23:B26" totalsRowShown="0" dataDxfId="8">
-  <autoFilter ref="A23:B26" xr:uid="{F9822EF2-40E4-4A6A-8A77-3DA3D90414BC}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{F9822EF2-40E4-4A6A-8A77-3DA3D90414BC}" name="Table4" displayName="Table4" ref="A23:B27" totalsRowShown="0" dataDxfId="8">
+  <autoFilter ref="A23:B27" xr:uid="{F9822EF2-40E4-4A6A-8A77-3DA3D90414BC}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{58EB44D0-5596-4751-B53E-6470D5AB8B54}" name="Column1" dataDxfId="7"/>
     <tableColumn id="2" xr3:uid="{7525EF9D-4911-4ADE-ADB2-08DA66A35B0F}" name="Column2" dataDxfId="6"/>
@@ -987,7 +991,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{162307CD-2880-4271-ADAB-61391DEF7FB6}">
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G34"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="28.6328125" bestFit="1" customWidth="1"/>
@@ -1411,17 +1415,28 @@
     </row>
     <row r="26" spans="1:4" ht="18" x14ac:dyDescent="0.4">
       <c r="A26" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B26" s="8">
+        <v>2.8899999999999999E-2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="18" x14ac:dyDescent="0.4">
+      <c r="A27" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="B26" s="2">
+      <c r="B27" s="2">
         <v>4866</v>
       </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A27" s="7"/>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A28" s="7"/>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A29" s="7"/>
+    </row>
+    <row r="34" spans="5:5" x14ac:dyDescent="0.35">
+      <c r="E34" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
